--- a/output/yearly_benthic_cover_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_39_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.07483279852831</v>
+        <v>45.52118652795701</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7529697696122</v>
+        <v>99.3783305098151</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03823044305288</v>
+        <v>87.94358996436348</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94415753069923</v>
+        <v>45.8739235726451</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228746893681387</v>
+        <v>2.228557237279074</v>
       </c>
       <c r="E3" t="n">
-        <v>5.715738552512784</v>
+        <v>5.670555837322973</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742915631227129</v>
+        <v>0.742852412426358</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97838991397628</v>
+        <v>33.95497800472383</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17411903644793</v>
+        <v>34.17121097161246</v>
       </c>
       <c r="I3" t="n">
-        <v>6.555097720037818</v>
+        <v>6.532607923334068</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643222695169556</v>
+        <v>4.642827577664737</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96176955694711</v>
+        <v>12.0564100356365</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85878023776161</v>
+        <v>48.83516102424361</v>
       </c>
       <c r="M3" t="n">
-        <v>106.764707325408</v>
+        <v>106.7654946325252</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.1821219883</v>
+        <v>87.01381607272417</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72011277553882</v>
+        <v>42.5744762561315</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187802959749263</v>
+        <v>2.183604379998106</v>
       </c>
       <c r="E4" t="n">
-        <v>6.523071398690663</v>
+        <v>6.465376190225859</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444705107126474</v>
+        <v>0.7444048174952757</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35417863377127</v>
+        <v>33.27006255597892</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24564349278177</v>
+        <v>34.24262160478267</v>
       </c>
       <c r="I4" t="n">
-        <v>5.474014300640346</v>
+        <v>5.455216414897857</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652940691954046</v>
+        <v>4.652530109345472</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8178780117</v>
+        <v>12.98618392727585</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27992316498233</v>
+        <v>44.25787848538892</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81791395222115</v>
+        <v>99.81853866879626</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.95529607564615</v>
+        <v>85.73626794891</v>
       </c>
       <c r="C5" t="n">
-        <v>42.34297735424781</v>
+        <v>42.14356876639759</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127759789715514</v>
+        <v>2.120804031634891</v>
       </c>
       <c r="E5" t="n">
-        <v>7.105676022255335</v>
+        <v>7.038442760021749</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457898218793648</v>
+        <v>0.7457228385638448</v>
       </c>
       <c r="G5" t="n">
-        <v>32.43878969980936</v>
+        <v>32.31321728779749</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30633180645077</v>
+        <v>34.30325057393685</v>
       </c>
       <c r="I5" t="n">
-        <v>4.569762548789771</v>
+        <v>4.554062715931138</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661186386746031</v>
+        <v>4.660767741024029</v>
       </c>
       <c r="K5" t="n">
-        <v>14.04470392435386</v>
+        <v>14.26373205109</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46026276860277</v>
+        <v>43.44116539320969</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84794404720444</v>
+        <v>99.84846621069728</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.62980849487218</v>
+        <v>84.13637425428035</v>
       </c>
       <c r="C6" t="n">
-        <v>41.72721699577306</v>
+        <v>41.25080193393431</v>
       </c>
       <c r="D6" t="n">
-        <v>2.063175754940962</v>
+        <v>2.042059542364923</v>
       </c>
       <c r="E6" t="n">
-        <v>7.525639619465696</v>
+        <v>7.410569720761035</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469101264886203</v>
+        <v>0.7468457451388463</v>
       </c>
       <c r="G6" t="n">
-        <v>31.45417295305855</v>
+        <v>31.11344222416956</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35786581847653</v>
+        <v>34.35490427638692</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81385593188795</v>
+        <v>3.800766838341282</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668188290553878</v>
+        <v>4.667785907117788</v>
       </c>
       <c r="K6" t="n">
-        <v>15.37019150512783</v>
+        <v>15.86362574571965</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77565365052161</v>
+        <v>42.75907057823683</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8730621514225</v>
+        <v>99.87349825789079</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.13729495630926</v>
+        <v>82.45639078334513</v>
       </c>
       <c r="C7" t="n">
-        <v>40.82708712815315</v>
+        <v>40.1608180446021</v>
       </c>
       <c r="D7" t="n">
-        <v>1.990685806271984</v>
+        <v>1.960000262937927</v>
       </c>
       <c r="E7" t="n">
-        <v>7.791603356504733</v>
+        <v>7.641340232648077</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747863115751658</v>
+        <v>0.7478032296176563</v>
       </c>
       <c r="G7" t="n">
-        <v>30.34902649264098</v>
+        <v>29.86316200635964</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40170332457626</v>
+        <v>34.39894856241218</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182268387115784</v>
+        <v>3.171366304259279</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674144473447863</v>
+        <v>4.673770185110351</v>
       </c>
       <c r="K7" t="n">
-        <v>16.86270504369073</v>
+        <v>17.54360921665488</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20426738560369</v>
+        <v>42.18999588212245</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89405955744758</v>
+        <v>99.89442314337941</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.105083371457</v>
+        <v>87.2913498777579</v>
       </c>
       <c r="C8" t="n">
-        <v>43.16490171338598</v>
+        <v>42.41877667701338</v>
       </c>
       <c r="D8" t="n">
-        <v>1.994969241763589</v>
+        <v>1.964210166489926</v>
       </c>
       <c r="E8" t="n">
-        <v>9.651428178586713</v>
+        <v>9.444383198579683</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494723216860047</v>
+        <v>0.7494094434187933</v>
       </c>
       <c r="G8" t="n">
-        <v>30.86191155657011</v>
+        <v>30.35188556987562</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47572679755621</v>
+        <v>34.47283439726449</v>
       </c>
       <c r="I8" t="n">
-        <v>5.687373264756858</v>
+        <v>5.62481808076194</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68420201053753</v>
+        <v>4.683809021367457</v>
       </c>
       <c r="K8" t="n">
-        <v>11.89491662854298</v>
+        <v>12.7086501222421</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75100959806951</v>
+        <v>44.6854811216083</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81082793999848</v>
+        <v>99.81290792086379</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.07673201097384</v>
+        <v>85.158192658068</v>
       </c>
       <c r="C9" t="n">
-        <v>42.01934289156169</v>
+        <v>41.15795589211329</v>
       </c>
       <c r="D9" t="n">
-        <v>1.903269323405619</v>
+        <v>1.867302862963281</v>
       </c>
       <c r="E9" t="n">
-        <v>9.999160085346116</v>
+        <v>9.761090881961477</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750850409470424</v>
+        <v>0.7507869581897714</v>
       </c>
       <c r="G9" t="n">
-        <v>29.44332589075475</v>
+        <v>28.85442901573198</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53911883563949</v>
+        <v>34.53620007672947</v>
       </c>
       <c r="I9" t="n">
-        <v>4.748192407167284</v>
+        <v>4.695964373805955</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69281505919015</v>
+        <v>4.692418488686069</v>
       </c>
       <c r="K9" t="n">
-        <v>13.92326798902615</v>
+        <v>14.84180734193199</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89940652872446</v>
+        <v>43.8439918192669</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84201740931231</v>
+        <v>99.84375505331218</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.93159749974292</v>
+        <v>82.82569056892295</v>
       </c>
       <c r="C10" t="n">
-        <v>40.61094236540813</v>
+        <v>39.55332490384114</v>
       </c>
       <c r="D10" t="n">
-        <v>1.80736251584821</v>
+        <v>1.762490094923936</v>
       </c>
       <c r="E10" t="n">
-        <v>10.15580593051522</v>
+        <v>9.866441399858713</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520321897798363</v>
+        <v>0.751971249283683</v>
       </c>
       <c r="G10" t="n">
-        <v>27.95966020281003</v>
+        <v>27.2348135611001</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59348072987246</v>
+        <v>34.5906774670494</v>
       </c>
       <c r="I10" t="n">
-        <v>3.963054744793187</v>
+        <v>3.919476488684076</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700201186123977</v>
+        <v>4.699820308023017</v>
       </c>
       <c r="K10" t="n">
-        <v>16.06840250025706</v>
+        <v>17.17430943107707</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18876090080238</v>
+        <v>43.14192221025384</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86810576646758</v>
+        <v>99.86955654517206</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.61500782527344</v>
+        <v>80.33741788624945</v>
       </c>
       <c r="C11" t="n">
-        <v>38.90869543459394</v>
+        <v>37.67181535703241</v>
       </c>
       <c r="D11" t="n">
-        <v>1.704786717342374</v>
+        <v>1.651884351690673</v>
       </c>
       <c r="E11" t="n">
-        <v>10.13058682948478</v>
+        <v>9.792379553701233</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530479241773893</v>
+        <v>0.7529917137598843</v>
       </c>
       <c r="G11" t="n">
-        <v>26.37282610278493</v>
+        <v>25.52568236971328</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6402045121599</v>
+        <v>34.63761883295467</v>
       </c>
       <c r="I11" t="n">
-        <v>3.307006213215379</v>
+        <v>3.27066285343045</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706549526108683</v>
+        <v>4.706198210999275</v>
       </c>
       <c r="K11" t="n">
-        <v>18.38499217472658</v>
+        <v>19.66258211375055</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59622753665742</v>
+        <v>42.55672818230915</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88991514597794</v>
+        <v>99.8911256530921</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.11721574318534</v>
+        <v>77.78748109263378</v>
       </c>
       <c r="C12" t="n">
-        <v>36.92276191020353</v>
+        <v>35.6272599248925</v>
       </c>
       <c r="D12" t="n">
-        <v>1.595191505292007</v>
+        <v>1.539746888608658</v>
       </c>
       <c r="E12" t="n">
-        <v>9.939164569303946</v>
+        <v>9.582417954329431</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539232881599494</v>
+        <v>0.7538721974107206</v>
       </c>
       <c r="G12" t="n">
-        <v>24.67740259924663</v>
+        <v>23.79288233353196</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68047125535766</v>
+        <v>34.67812108089314</v>
       </c>
       <c r="I12" t="n">
-        <v>2.759041974825464</v>
+        <v>2.728739404042861</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712020550999683</v>
+        <v>4.711701233817003</v>
       </c>
       <c r="K12" t="n">
-        <v>20.88278425681467</v>
+        <v>22.21251890736623</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1025925492814</v>
+        <v>42.06936942181265</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90813871629959</v>
+        <v>99.90914825407138</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.64227345969769</v>
+        <v>75.19142997146186</v>
       </c>
       <c r="C13" t="n">
-        <v>34.87393995279619</v>
+        <v>33.45185983660369</v>
       </c>
       <c r="D13" t="n">
-        <v>1.487653565771132</v>
+        <v>1.426699746686937</v>
       </c>
       <c r="E13" t="n">
-        <v>9.652711449107942</v>
+        <v>9.258257535933911</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546779442581557</v>
+        <v>0.7546329211425384</v>
       </c>
       <c r="G13" t="n">
-        <v>23.01380483092459</v>
+        <v>22.04602551843809</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71518543587516</v>
+        <v>34.71311437255676</v>
       </c>
       <c r="I13" t="n">
-        <v>2.301503082147237</v>
+        <v>2.276244119562763</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716737151613473</v>
+        <v>4.716455757140864</v>
       </c>
       <c r="K13" t="n">
-        <v>23.35772654030233</v>
+        <v>24.80857002853814</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69169345204523</v>
+        <v>41.6637718180792</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92335994514373</v>
+        <v>99.92420168322103</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.53068156993059</v>
+        <v>82.41251020470165</v>
       </c>
       <c r="C14" t="n">
-        <v>38.99763952985018</v>
+        <v>37.9896702739476</v>
       </c>
       <c r="D14" t="n">
-        <v>1.489566169872861</v>
+        <v>1.428366798909105</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9806240971138</v>
+        <v>11.76447504517142</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556481971213779</v>
+        <v>0.7555146851514222</v>
       </c>
       <c r="G14" t="n">
-        <v>24.82193844116251</v>
+        <v>24.08570343805981</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5383629441387</v>
+        <v>36.76759337325507</v>
       </c>
       <c r="I14" t="n">
-        <v>3.221740488512741</v>
+        <v>2.888890081958424</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722801232008612</v>
+        <v>4.721966782196387</v>
       </c>
       <c r="K14" t="n">
-        <v>16.46931843006941</v>
+        <v>17.58748979529836</v>
       </c>
       <c r="L14" t="n">
-        <v>44.42578858103841</v>
+        <v>44.326655982502</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89274654095799</v>
+        <v>99.90381605174795</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.69886637507634</v>
+        <v>81.44884629316707</v>
       </c>
       <c r="C15" t="n">
-        <v>38.66342566715419</v>
+        <v>37.47163078936251</v>
       </c>
       <c r="D15" t="n">
-        <v>1.458787137719248</v>
+        <v>1.392815261466511</v>
       </c>
       <c r="E15" t="n">
-        <v>12.18101615045654</v>
+        <v>11.8732919171749</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564668096286934</v>
+        <v>0.7562597851921419</v>
       </c>
       <c r="G15" t="n">
-        <v>24.30904062108061</v>
+        <v>23.48621891611253</v>
       </c>
       <c r="H15" t="n">
-        <v>36.57794586250845</v>
+        <v>36.80385413146136</v>
       </c>
       <c r="I15" t="n">
-        <v>2.687692233503459</v>
+        <v>2.409782624308745</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727917560179334</v>
+        <v>4.726623657450885</v>
       </c>
       <c r="K15" t="n">
-        <v>17.30113362492365</v>
+        <v>18.55115370683294</v>
       </c>
       <c r="L15" t="n">
-        <v>43.9459479165746</v>
+        <v>43.89696855708348</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91050720865243</v>
+        <v>99.91975305327892</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.15775970478911</v>
+        <v>78.71570977192916</v>
       </c>
       <c r="C16" t="n">
-        <v>36.53749463658446</v>
+        <v>35.11014138986216</v>
       </c>
       <c r="D16" t="n">
-        <v>1.362373649778757</v>
+        <v>1.290333944083595</v>
       </c>
       <c r="E16" t="n">
-        <v>11.74959262982893</v>
+        <v>11.33464928860566</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571720319154484</v>
+        <v>0.7569034420966066</v>
       </c>
       <c r="G16" t="n">
-        <v>22.70241869923548</v>
+        <v>21.75813715146233</v>
       </c>
       <c r="H16" t="n">
-        <v>36.61204594766436</v>
+        <v>36.83517809617094</v>
       </c>
       <c r="I16" t="n">
-        <v>2.241831546894604</v>
+        <v>2.009861336406233</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732325199471553</v>
+        <v>4.73064651310379</v>
       </c>
       <c r="K16" t="n">
-        <v>19.84224029521088</v>
+        <v>21.28429022807085</v>
       </c>
       <c r="L16" t="n">
-        <v>43.54560695060734</v>
+        <v>43.53862997583619</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92534188240268</v>
+        <v>99.93306159376921</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.86439064394361</v>
+        <v>80.5124651503335</v>
       </c>
       <c r="C17" t="n">
-        <v>37.76263525977344</v>
+        <v>36.41950696757064</v>
       </c>
       <c r="D17" t="n">
-        <v>1.363637173831593</v>
+        <v>1.291396161988575</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54639257406451</v>
+        <v>12.14994531054097</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578742658984788</v>
+        <v>0.7575265338103624</v>
       </c>
       <c r="G17" t="n">
-        <v>23.1297539418134</v>
+        <v>22.25061992280187</v>
       </c>
       <c r="H17" t="n">
-        <v>37.05228157817713</v>
+        <v>37.34007246291105</v>
       </c>
       <c r="I17" t="n">
-        <v>2.277736948292998</v>
+        <v>1.988363921965904</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736714161865493</v>
+        <v>4.734540836314763</v>
       </c>
       <c r="K17" t="n">
-        <v>18.1356093560564</v>
+        <v>19.48753484966651</v>
       </c>
       <c r="L17" t="n">
-        <v>44.02590116969554</v>
+        <v>44.02673390196192</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92414578552538</v>
+        <v>99.93377571919908</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.38714666181764</v>
+        <v>77.92299758813508</v>
       </c>
       <c r="C18" t="n">
-        <v>35.63676632741158</v>
+        <v>34.13618202277195</v>
       </c>
       <c r="D18" t="n">
-        <v>1.27345118691413</v>
+        <v>1.198554343275483</v>
       </c>
       <c r="E18" t="n">
-        <v>12.03322463313607</v>
+        <v>11.55281177686859</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584787631054037</v>
+        <v>0.7580638544364798</v>
       </c>
       <c r="G18" t="n">
-        <v>21.6000364139909</v>
+        <v>20.65096516004832</v>
       </c>
       <c r="H18" t="n">
-        <v>37.08183529405327</v>
+        <v>37.36655812409855</v>
       </c>
       <c r="I18" t="n">
-        <v>1.899628101209088</v>
+        <v>1.658145239179663</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740492269408773</v>
+        <v>4.737899090227997</v>
       </c>
       <c r="K18" t="n">
-        <v>20.61285333818238</v>
+        <v>22.07700241186494</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68710986362012</v>
+        <v>43.73158323419739</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93672952921408</v>
+        <v>99.94476766883427</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.4217646918006</v>
+        <v>76.89085677422925</v>
       </c>
       <c r="C19" t="n">
-        <v>34.96364626340853</v>
+        <v>33.34812856435929</v>
       </c>
       <c r="D19" t="n">
-        <v>1.239066277521729</v>
+        <v>1.161785364731118</v>
       </c>
       <c r="E19" t="n">
-        <v>11.97232612911187</v>
+        <v>11.43051648837679</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758989462355541</v>
+        <v>0.7585215453069061</v>
       </c>
       <c r="G19" t="n">
-        <v>21.01680613190415</v>
+        <v>20.01743953048433</v>
       </c>
       <c r="H19" t="n">
-        <v>37.10680325149594</v>
+        <v>37.38911866753108</v>
       </c>
       <c r="I19" t="n">
-        <v>1.584089299689243</v>
+        <v>1.39271551963087</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743684139722131</v>
+        <v>4.740759658168161</v>
       </c>
       <c r="K19" t="n">
-        <v>21.57823530819939</v>
+        <v>23.10914322577074</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40535098113629</v>
+        <v>43.49633237130406</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9472325527442</v>
+        <v>99.9536041614341</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.85429809565436</v>
+        <v>74.27909372166738</v>
       </c>
       <c r="C20" t="n">
-        <v>32.63973380748164</v>
+        <v>30.9499325873971</v>
       </c>
       <c r="D20" t="n">
-        <v>1.146788818058776</v>
+        <v>1.069293150476883</v>
       </c>
       <c r="E20" t="n">
-        <v>11.30084658470516</v>
+        <v>10.71404216567275</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7594300017147622</v>
+        <v>0.7589168095153885</v>
       </c>
       <c r="G20" t="n">
-        <v>19.45161344523327</v>
+        <v>18.42380841575321</v>
       </c>
       <c r="H20" t="n">
-        <v>37.12834110957954</v>
+        <v>37.40860206979885</v>
       </c>
       <c r="I20" t="n">
-        <v>1.320840625645606</v>
+        <v>1.161201050979124</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746437510717262</v>
+        <v>4.743230059471176</v>
       </c>
       <c r="K20" t="n">
-        <v>24.14570190434565</v>
+        <v>25.72090627833261</v>
       </c>
       <c r="L20" t="n">
-        <v>43.17056180762577</v>
+        <v>43.2904745920583</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95599751945305</v>
+        <v>99.96131345778801</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.9339474687895</v>
+        <v>80.66686461178038</v>
       </c>
       <c r="C21" t="n">
-        <v>36.33523853736412</v>
+        <v>34.98817639476347</v>
       </c>
       <c r="D21" t="n">
-        <v>1.147715619597359</v>
+        <v>1.069998630240324</v>
       </c>
       <c r="E21" t="n">
-        <v>13.3152867039447</v>
+        <v>12.86654811522397</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7600437510668242</v>
+        <v>0.7594175145381503</v>
       </c>
       <c r="G21" t="n">
-        <v>21.14155755112279</v>
+        <v>20.31529602938357</v>
       </c>
       <c r="H21" t="n">
-        <v>38.83257103526294</v>
+        <v>39.31261514263566</v>
       </c>
       <c r="I21" t="n">
-        <v>1.986499363627234</v>
+        <v>1.596629713895267</v>
       </c>
       <c r="J21" t="n">
-        <v>4.75027344416765</v>
+        <v>4.746359465863438</v>
       </c>
       <c r="K21" t="n">
-        <v>18.06605253121051</v>
+        <v>19.33313538821961</v>
       </c>
       <c r="L21" t="n">
-        <v>45.53254575713407</v>
+        <v>45.62550231662834</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9338368257087</v>
+        <v>99.94681409961142</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_39_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.52118652795701</v>
+        <v>45.34662912469052</v>
       </c>
       <c r="M2" t="n">
-        <v>99.3783305098151</v>
+        <v>100.0180103668217</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.94358996436348</v>
+        <v>88.03576625631523</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8739235726451</v>
+        <v>45.93025939205329</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228557237279074</v>
+        <v>2.228751113561086</v>
       </c>
       <c r="E3" t="n">
-        <v>5.670555837322973</v>
+        <v>5.707715936722967</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742852412426358</v>
+        <v>0.7429170378536956</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95497800472383</v>
+        <v>33.97358123110738</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17121097161246</v>
+        <v>34.17418374126999</v>
       </c>
       <c r="I3" t="n">
-        <v>6.532607923334068</v>
+        <v>6.565385709214508</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642827577664737</v>
+        <v>4.643231486585597</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0564100356365</v>
+        <v>11.96423374368477</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83516102424361</v>
+        <v>48.86984535251156</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7654946325252</v>
+        <v>106.7643384882496</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.01381607272417</v>
+        <v>87.08677734064328</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5744762561315</v>
+        <v>42.61583552985299</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183604379998106</v>
+        <v>2.182855658241732</v>
       </c>
       <c r="E4" t="n">
-        <v>6.465376190225859</v>
+        <v>6.503952750881293</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444048174952757</v>
+        <v>0.7444760743076431</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27006255597892</v>
+        <v>33.27398181422167</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24262160478267</v>
+        <v>34.24589941815158</v>
       </c>
       <c r="I4" t="n">
-        <v>5.455216414897857</v>
+        <v>5.482636160416608</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652530109345472</v>
+        <v>4.652975464422768</v>
       </c>
       <c r="K4" t="n">
-        <v>12.98618392727585</v>
+        <v>12.91322265935671</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25787848538892</v>
+        <v>44.28856998553434</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81853866879626</v>
+        <v>99.81762817474404</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.73626794891</v>
+        <v>85.85078789880393</v>
       </c>
       <c r="C5" t="n">
-        <v>42.14356876639759</v>
+        <v>42.23075410031529</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120804031634891</v>
+        <v>2.122322762506882</v>
       </c>
       <c r="E5" t="n">
-        <v>7.038442760021749</v>
+        <v>7.086421734842608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457228385638448</v>
+        <v>0.7457990884551627</v>
       </c>
       <c r="G5" t="n">
-        <v>32.31321728779749</v>
+        <v>32.35125911185757</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30325057393685</v>
+        <v>34.30675806893749</v>
       </c>
       <c r="I5" t="n">
-        <v>4.554062715931138</v>
+        <v>4.576982829359456</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660767741024029</v>
+        <v>4.661244302844766</v>
       </c>
       <c r="K5" t="n">
-        <v>14.26373205109</v>
+        <v>14.14921210119606</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44116539320969</v>
+        <v>43.46773834958819</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84846621069728</v>
+        <v>99.84770455109954</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.13637425428035</v>
+        <v>84.36042360001019</v>
       </c>
       <c r="C6" t="n">
-        <v>41.25080193393431</v>
+        <v>41.45113045850174</v>
       </c>
       <c r="D6" t="n">
-        <v>2.042059542364923</v>
+        <v>2.04930359242444</v>
       </c>
       <c r="E6" t="n">
-        <v>7.410569720761035</v>
+        <v>7.479262754808554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468457451388463</v>
+        <v>0.7469247683038214</v>
       </c>
       <c r="G6" t="n">
-        <v>31.11344222416956</v>
+        <v>31.2382040510526</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35490427638692</v>
+        <v>34.35853934197578</v>
       </c>
       <c r="I6" t="n">
-        <v>3.800766838341282</v>
+        <v>3.819909289546114</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667785907117788</v>
+        <v>4.668279801898882</v>
       </c>
       <c r="K6" t="n">
-        <v>15.86362574571965</v>
+        <v>15.63957639998981</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75907057823683</v>
+        <v>42.7821547295818</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87349825789079</v>
+        <v>99.87286158807335</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.45639078334513</v>
+        <v>82.58034131339923</v>
       </c>
       <c r="C7" t="n">
-        <v>40.1608180446021</v>
+        <v>40.26415583685984</v>
       </c>
       <c r="D7" t="n">
-        <v>1.960000262937927</v>
+        <v>1.962342127660708</v>
       </c>
       <c r="E7" t="n">
-        <v>7.641340232648077</v>
+        <v>7.693108451387379</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478032296176563</v>
+        <v>0.7478857367470914</v>
       </c>
       <c r="G7" t="n">
-        <v>29.86316200635964</v>
+        <v>29.9126220382606</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39894856241218</v>
+        <v>34.4027438903662</v>
       </c>
       <c r="I7" t="n">
-        <v>3.171366304259279</v>
+        <v>3.187353214307913</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673770185110351</v>
+        <v>4.67428585466932</v>
       </c>
       <c r="K7" t="n">
-        <v>17.54360921665488</v>
+        <v>17.41965868660078</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18999588212245</v>
+        <v>42.2100768851631</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89442314337941</v>
+        <v>99.89389140862373</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.2913498777579</v>
+        <v>87.37517988982265</v>
       </c>
       <c r="C8" t="n">
-        <v>42.41877667701338</v>
+        <v>42.57950443925118</v>
       </c>
       <c r="D8" t="n">
-        <v>1.964210166489926</v>
+        <v>1.966493923822817</v>
       </c>
       <c r="E8" t="n">
-        <v>9.444383198579683</v>
+        <v>9.529713025471544</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494094434187933</v>
+        <v>0.7494680648680412</v>
       </c>
       <c r="G8" t="n">
-        <v>30.35188556987562</v>
+        <v>30.42391637813508</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47283439726449</v>
+        <v>34.47553098392989</v>
       </c>
       <c r="I8" t="n">
-        <v>5.62481808076194</v>
+        <v>5.545882108170019</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683809021367457</v>
+        <v>4.684175405425256</v>
       </c>
       <c r="K8" t="n">
-        <v>12.7086501222421</v>
+        <v>12.62482011017735</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6854811216083</v>
+        <v>44.6112030084574</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81290792086379</v>
+        <v>99.81552755788593</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.158192658068</v>
+        <v>85.16769121373427</v>
       </c>
       <c r="C9" t="n">
-        <v>41.15795589211329</v>
+        <v>41.23236412012162</v>
       </c>
       <c r="D9" t="n">
-        <v>1.867302862963281</v>
+        <v>1.866315339660167</v>
       </c>
       <c r="E9" t="n">
-        <v>9.761090881961477</v>
+        <v>9.815900540534237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507869581897714</v>
+        <v>0.7508261677114876</v>
       </c>
       <c r="G9" t="n">
-        <v>28.85442901573198</v>
+        <v>28.87403878608053</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53620007672947</v>
+        <v>34.53800371472843</v>
       </c>
       <c r="I9" t="n">
-        <v>4.695964373805955</v>
+        <v>4.629943116822635</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692418488686069</v>
+        <v>4.692663548196795</v>
       </c>
       <c r="K9" t="n">
-        <v>14.84180734193199</v>
+        <v>14.83230878626572</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8439918192669</v>
+        <v>43.78127481283017</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84375505331218</v>
+        <v>99.84594771921751</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.82569056892295</v>
+        <v>82.79097502159101</v>
       </c>
       <c r="C10" t="n">
-        <v>39.55332490384114</v>
+        <v>39.57341229695739</v>
       </c>
       <c r="D10" t="n">
-        <v>1.762490094923936</v>
+        <v>1.759677279690749</v>
       </c>
       <c r="E10" t="n">
-        <v>9.866441399858713</v>
+        <v>9.899084941671161</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751971249283683</v>
+        <v>0.7519943341526002</v>
       </c>
       <c r="G10" t="n">
-        <v>27.2348135611001</v>
+        <v>27.22422569490697</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5906774670494</v>
+        <v>34.59173937101961</v>
       </c>
       <c r="I10" t="n">
-        <v>3.919476488684076</v>
+        <v>3.864288811696165</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699820308023017</v>
+        <v>4.699964588453749</v>
       </c>
       <c r="K10" t="n">
-        <v>17.17430943107707</v>
+        <v>17.209024978409</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14192221025384</v>
+        <v>43.08895319361076</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86955654517206</v>
+        <v>99.87139046897714</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.33741788624945</v>
+        <v>80.34335918198552</v>
       </c>
       <c r="C11" t="n">
-        <v>37.67181535703241</v>
+        <v>37.72407319021825</v>
       </c>
       <c r="D11" t="n">
-        <v>1.651884351690673</v>
+        <v>1.651114626772972</v>
       </c>
       <c r="E11" t="n">
-        <v>9.792379553701233</v>
+        <v>9.825789275326683</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529917137598843</v>
+        <v>0.7530003672737516</v>
       </c>
       <c r="G11" t="n">
-        <v>25.52568236971328</v>
+        <v>25.54463694350204</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63761883295467</v>
+        <v>34.63801689459257</v>
       </c>
       <c r="I11" t="n">
-        <v>3.27066285343045</v>
+        <v>3.22454877905656</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706198210999275</v>
+        <v>4.706252295460946</v>
       </c>
       <c r="K11" t="n">
-        <v>19.66258211375055</v>
+        <v>19.65664081801448</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55672818230915</v>
+        <v>42.51194463588682</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8911256530921</v>
+        <v>99.89265864411955</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.78748109263378</v>
+        <v>77.81970091400562</v>
       </c>
       <c r="C12" t="n">
-        <v>35.6272599248925</v>
+        <v>35.69873694198674</v>
       </c>
       <c r="D12" t="n">
-        <v>1.539746888608658</v>
+        <v>1.540335542804768</v>
       </c>
       <c r="E12" t="n">
-        <v>9.582417954329431</v>
+        <v>9.614912608164634</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538721974107206</v>
+        <v>0.7538680725607427</v>
       </c>
       <c r="G12" t="n">
-        <v>23.79288233353196</v>
+        <v>23.83075746171691</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67812108089314</v>
+        <v>34.67793133779416</v>
       </c>
       <c r="I12" t="n">
-        <v>2.728739404042861</v>
+        <v>2.690220437459763</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711701233817003</v>
+        <v>4.71167545350464</v>
       </c>
       <c r="K12" t="n">
-        <v>22.21251890736623</v>
+        <v>22.18029908599438</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06936942181265</v>
+        <v>42.03139317260066</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90914825407138</v>
+        <v>99.91042920058177</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.19142997146186</v>
+        <v>75.28289260336771</v>
       </c>
       <c r="C13" t="n">
-        <v>33.45185983660369</v>
+        <v>33.57670710203411</v>
       </c>
       <c r="D13" t="n">
-        <v>1.426699746686937</v>
+        <v>1.430066531816328</v>
       </c>
       <c r="E13" t="n">
-        <v>9.258257535933911</v>
+        <v>9.300616537106192</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546329211425384</v>
+        <v>0.7546171310483727</v>
       </c>
       <c r="G13" t="n">
-        <v>22.04602551843809</v>
+        <v>22.12476939393267</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71311437255676</v>
+        <v>34.71238802822514</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276244119562763</v>
+        <v>2.244077912186696</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716455757140864</v>
+        <v>4.716357069052327</v>
       </c>
       <c r="K13" t="n">
-        <v>24.80857002853814</v>
+        <v>24.71710739663229</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6637718180792</v>
+        <v>41.63145715584861</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92420168322103</v>
+        <v>99.925271654515</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.41251020470165</v>
+        <v>82.66492735694052</v>
       </c>
       <c r="C14" t="n">
-        <v>37.9896702739476</v>
+        <v>38.19156817764269</v>
       </c>
       <c r="D14" t="n">
-        <v>1.428366798909105</v>
+        <v>1.431740089362822</v>
       </c>
       <c r="E14" t="n">
-        <v>11.76447504517142</v>
+        <v>11.84678058916506</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555146851514222</v>
+        <v>0.7555002334539475</v>
       </c>
       <c r="G14" t="n">
-        <v>24.08570343805981</v>
+        <v>24.20224154086701</v>
       </c>
       <c r="H14" t="n">
-        <v>36.76759337325507</v>
+        <v>36.80459103116451</v>
       </c>
       <c r="I14" t="n">
-        <v>2.888890081958424</v>
+        <v>2.902197413840002</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721966782196387</v>
+        <v>4.721876459087169</v>
       </c>
       <c r="K14" t="n">
-        <v>17.58748979529836</v>
+        <v>17.33507264305946</v>
       </c>
       <c r="L14" t="n">
-        <v>44.326655982502</v>
+        <v>44.37673234455573</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90381605174795</v>
+        <v>99.90337316525789</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.44884629316707</v>
+        <v>81.79227145758962</v>
       </c>
       <c r="C15" t="n">
-        <v>37.47163078936251</v>
+        <v>37.73994017519401</v>
       </c>
       <c r="D15" t="n">
-        <v>1.392815261466511</v>
+        <v>1.396716434635678</v>
       </c>
       <c r="E15" t="n">
-        <v>11.8732919171749</v>
+        <v>11.98723749399666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562597851921419</v>
+        <v>0.7562456088390843</v>
       </c>
       <c r="G15" t="n">
-        <v>23.48621891611253</v>
+        <v>23.63697480549315</v>
       </c>
       <c r="H15" t="n">
-        <v>36.80385413146136</v>
+        <v>36.86767812820634</v>
       </c>
       <c r="I15" t="n">
-        <v>2.409782624308745</v>
+        <v>2.420883931174449</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726623657450885</v>
+        <v>4.726535055244274</v>
       </c>
       <c r="K15" t="n">
-        <v>18.55115370683294</v>
+        <v>18.20772854241036</v>
       </c>
       <c r="L15" t="n">
-        <v>43.89696855708348</v>
+        <v>43.97171468756673</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91975305327892</v>
+        <v>99.9193834051711</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.71570977192916</v>
+        <v>79.15368705774775</v>
       </c>
       <c r="C16" t="n">
-        <v>35.11014138986216</v>
+        <v>35.47482382245246</v>
       </c>
       <c r="D16" t="n">
-        <v>1.290333944083595</v>
+        <v>1.298271551068571</v>
       </c>
       <c r="E16" t="n">
-        <v>11.33464928860566</v>
+        <v>11.47885978869176</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569034420966066</v>
+        <v>0.7568886404229558</v>
       </c>
       <c r="G16" t="n">
-        <v>21.75813715146233</v>
+        <v>21.97096789463984</v>
       </c>
       <c r="H16" t="n">
-        <v>36.83517809617094</v>
+        <v>36.89902651712041</v>
       </c>
       <c r="I16" t="n">
-        <v>2.009861336406233</v>
+        <v>2.019118663160726</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73064651310379</v>
+        <v>4.730554002643471</v>
       </c>
       <c r="K16" t="n">
-        <v>21.28429022807085</v>
+        <v>20.84631294225226</v>
       </c>
       <c r="L16" t="n">
-        <v>43.53862997583619</v>
+        <v>43.61161645942933</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93306159376921</v>
+        <v>99.93275322413405</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.5124651503335</v>
+        <v>81.07501640234396</v>
       </c>
       <c r="C17" t="n">
-        <v>36.41950696757064</v>
+        <v>36.86320492340675</v>
       </c>
       <c r="D17" t="n">
-        <v>1.291396161988575</v>
+        <v>1.299341734472578</v>
       </c>
       <c r="E17" t="n">
-        <v>12.14994531054097</v>
+        <v>12.33506847227561</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575265338103624</v>
+        <v>0.757512554319086</v>
       </c>
       <c r="G17" t="n">
-        <v>22.25061992280187</v>
+        <v>22.50166901792072</v>
       </c>
       <c r="H17" t="n">
-        <v>37.34007246291105</v>
+        <v>37.44203304798623</v>
       </c>
       <c r="I17" t="n">
-        <v>1.988363921965904</v>
+        <v>2.004938110875454</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734540836314763</v>
+        <v>4.734453464494285</v>
       </c>
       <c r="K17" t="n">
-        <v>19.48753484966651</v>
+        <v>18.92498359765604</v>
       </c>
       <c r="L17" t="n">
-        <v>44.02673390196192</v>
+        <v>44.1450352531519</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93377571919908</v>
+        <v>99.9332237742147</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.92299758813508</v>
+        <v>78.5057237554678</v>
       </c>
       <c r="C18" t="n">
-        <v>34.13618202277195</v>
+        <v>34.60276275862231</v>
       </c>
       <c r="D18" t="n">
-        <v>1.198554343275483</v>
+        <v>1.20781474654664</v>
       </c>
       <c r="E18" t="n">
-        <v>11.55281177686859</v>
+        <v>11.74483468628373</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580638544364798</v>
+        <v>0.7580503226035161</v>
       </c>
       <c r="G18" t="n">
-        <v>20.65096516004832</v>
+        <v>20.91662796684367</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36655812409855</v>
+        <v>37.46861364755912</v>
       </c>
       <c r="I18" t="n">
-        <v>1.658145239179663</v>
+        <v>1.671967869359144</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737899090227997</v>
+        <v>4.737814516271973</v>
       </c>
       <c r="K18" t="n">
-        <v>22.07700241186494</v>
+        <v>21.4942762445322</v>
       </c>
       <c r="L18" t="n">
-        <v>43.73158323419739</v>
+        <v>43.84726827154339</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94476766883427</v>
+        <v>99.94430727469791</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.89085677422925</v>
+        <v>77.54042032526714</v>
       </c>
       <c r="C19" t="n">
-        <v>33.34812856435929</v>
+        <v>33.89048850298754</v>
       </c>
       <c r="D19" t="n">
-        <v>1.161785364731118</v>
+        <v>1.173940521736253</v>
       </c>
       <c r="E19" t="n">
-        <v>11.43051648837679</v>
+        <v>11.64840355754382</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585215453069061</v>
+        <v>0.7585058211152315</v>
       </c>
       <c r="G19" t="n">
-        <v>20.01743953048433</v>
+        <v>20.33000277448704</v>
       </c>
       <c r="H19" t="n">
-        <v>37.38911866753108</v>
+        <v>37.49112784911487</v>
       </c>
       <c r="I19" t="n">
-        <v>1.39271551963087</v>
+        <v>1.397778419299705</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740759658168161</v>
+        <v>4.740661381970193</v>
       </c>
       <c r="K19" t="n">
-        <v>23.10914322577074</v>
+        <v>22.45957967473288</v>
       </c>
       <c r="L19" t="n">
-        <v>43.49633237130406</v>
+        <v>43.60336718813609</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9536041614341</v>
+        <v>99.95343536585651</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.27909372166738</v>
+        <v>74.94118437341143</v>
       </c>
       <c r="C20" t="n">
-        <v>30.9499325873971</v>
+        <v>31.50575261459606</v>
       </c>
       <c r="D20" t="n">
-        <v>1.069293150476883</v>
+        <v>1.082461153837158</v>
       </c>
       <c r="E20" t="n">
-        <v>10.71404216567275</v>
+        <v>10.93493771288681</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589168095153885</v>
+        <v>0.7588990082173657</v>
       </c>
       <c r="G20" t="n">
-        <v>18.42380841575321</v>
+        <v>18.74578639489882</v>
       </c>
       <c r="H20" t="n">
-        <v>37.40860206979885</v>
+        <v>37.5105621467885</v>
       </c>
       <c r="I20" t="n">
-        <v>1.161201050979124</v>
+        <v>1.165419155424245</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743230059471176</v>
+        <v>4.743118801358532</v>
       </c>
       <c r="K20" t="n">
-        <v>25.72090627833261</v>
+        <v>25.05881562658856</v>
       </c>
       <c r="L20" t="n">
-        <v>43.2904745920583</v>
+        <v>43.39660458050148</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96131345778801</v>
+        <v>99.96117282168612</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.66686461178038</v>
+        <v>81.44647046372278</v>
       </c>
       <c r="C21" t="n">
-        <v>34.98817639476347</v>
+        <v>35.6122535822147</v>
       </c>
       <c r="D21" t="n">
-        <v>1.069998630240324</v>
+        <v>1.083177657813339</v>
       </c>
       <c r="E21" t="n">
-        <v>12.86654811522397</v>
+        <v>13.12339198277447</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594175145381503</v>
+        <v>0.7594013395527491</v>
       </c>
       <c r="G21" t="n">
-        <v>20.31529602938357</v>
+        <v>20.6698551073802</v>
       </c>
       <c r="H21" t="n">
-        <v>39.31261514263566</v>
+        <v>39.4470516619848</v>
       </c>
       <c r="I21" t="n">
-        <v>1.596629713895267</v>
+        <v>1.617334342012535</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746359465863438</v>
+        <v>4.746258372204679</v>
       </c>
       <c r="K21" t="n">
-        <v>19.33313538821961</v>
+        <v>18.55352953627722</v>
       </c>
       <c r="L21" t="n">
-        <v>45.62550231662834</v>
+        <v>45.78034139809846</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94681409961142</v>
+        <v>99.94612451659039</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_39_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.34662912469052</v>
+        <v>43.88376949288556</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0180103668217</v>
+        <v>94.44431855912202</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03576625631523</v>
+        <v>81.45905215551672</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93025939205329</v>
+        <v>43.21460771107228</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228751113561086</v>
+        <v>2.179488698828657</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707715936722967</v>
+        <v>4.144717538763495</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429170378536956</v>
+        <v>0.7376203786306564</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97358123110738</v>
+        <v>32.78314251154772</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17418374126999</v>
+        <v>33.93053741701019</v>
       </c>
       <c r="I3" t="n">
-        <v>6.565385709214508</v>
+        <v>3.073418244294402</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643231486585597</v>
+        <v>4.610127366441603</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96423374368477</v>
+        <v>18.54094784448327</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86984535251156</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643384882496</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08677734064328</v>
+        <v>88.60441143130662</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61583552985299</v>
+        <v>42.79241242624411</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182855658241732</v>
+        <v>2.185273692734711</v>
       </c>
       <c r="E4" t="n">
-        <v>6.503952750881293</v>
+        <v>6.517866190297004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444760743076431</v>
+        <v>0.7395782366354503</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27398181422167</v>
+        <v>33.46327775633018</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24589941815158</v>
+        <v>34.02059888523071</v>
       </c>
       <c r="I4" t="n">
-        <v>5.482636160416608</v>
+        <v>7.055452691107005</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652975464422768</v>
+        <v>4.622363978971564</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91322265935671</v>
+        <v>11.39558856869337</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28856998553434</v>
+        <v>45.57743983662347</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81762817474404</v>
+        <v>99.76544083156094</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.85078789880393</v>
+        <v>87.61546500474694</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23075410031529</v>
+        <v>42.89697343431361</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122322762506882</v>
+        <v>2.138805805425343</v>
       </c>
       <c r="E5" t="n">
-        <v>7.086421734842608</v>
+        <v>7.36139047102577</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457990884551627</v>
+        <v>0.7412362891680184</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35125911185757</v>
+        <v>32.7517111342851</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30675806893749</v>
+        <v>34.09686930172884</v>
       </c>
       <c r="I5" t="n">
-        <v>4.576982829359456</v>
+        <v>5.892725195813751</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661244302844766</v>
+        <v>4.632726807300116</v>
       </c>
       <c r="K5" t="n">
-        <v>14.14921210119606</v>
+        <v>12.38453499525307</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46773834958819</v>
+        <v>44.52250677345811</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84770455109954</v>
+        <v>99.80401520302479</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.36042360001019</v>
+        <v>86.41375819632552</v>
       </c>
       <c r="C6" t="n">
-        <v>41.45113045850174</v>
+        <v>42.60987094645693</v>
       </c>
       <c r="D6" t="n">
-        <v>2.04930359242444</v>
+        <v>2.081918616728672</v>
       </c>
       <c r="E6" t="n">
-        <v>7.479262754808554</v>
+        <v>7.985582143647192</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469247683038214</v>
+        <v>0.7426430196485706</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2382040510526</v>
+        <v>31.88059288376004</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35853934197578</v>
+        <v>34.16157890383425</v>
       </c>
       <c r="I6" t="n">
-        <v>3.819909289546114</v>
+        <v>4.91992375590322</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668279801898882</v>
+        <v>4.641518872803567</v>
       </c>
       <c r="K6" t="n">
-        <v>15.63957639998981</v>
+        <v>13.5862418036745</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7821547295818</v>
+        <v>43.64020043887376</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87286158807335</v>
+        <v>99.83631318900518</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.58034131339923</v>
+        <v>85.0672033307255</v>
       </c>
       <c r="C7" t="n">
-        <v>40.26415583685984</v>
+        <v>42.02750454205992</v>
       </c>
       <c r="D7" t="n">
-        <v>1.962342127660708</v>
+        <v>2.018330528880291</v>
       </c>
       <c r="E7" t="n">
-        <v>7.693108451387379</v>
+        <v>8.426100627076325</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478857367470914</v>
+        <v>0.7438380311796032</v>
       </c>
       <c r="G7" t="n">
-        <v>29.9126220382606</v>
+        <v>30.90686320736356</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4027438903662</v>
+        <v>34.21654943426175</v>
       </c>
       <c r="I7" t="n">
-        <v>3.187353214307913</v>
+        <v>4.106533807091458</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67428585466932</v>
+        <v>4.64898769487252</v>
       </c>
       <c r="K7" t="n">
-        <v>17.41965868660078</v>
+        <v>14.9327966692745</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2100768851631</v>
+        <v>42.90303423989049</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89389140862373</v>
+        <v>99.86333545122491</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.37517988982265</v>
+        <v>83.48782361156833</v>
       </c>
       <c r="C8" t="n">
-        <v>42.57950443925118</v>
+        <v>41.0861045929942</v>
       </c>
       <c r="D8" t="n">
-        <v>1.966493923822817</v>
+        <v>1.943897973918072</v>
       </c>
       <c r="E8" t="n">
-        <v>9.529713025471544</v>
+        <v>8.686492805395257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494680648680412</v>
+        <v>0.7448557362272459</v>
       </c>
       <c r="G8" t="n">
-        <v>30.42391637813508</v>
+        <v>29.76707130436534</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47553098392989</v>
+        <v>34.26336386645331</v>
       </c>
       <c r="I8" t="n">
-        <v>5.545882108170019</v>
+        <v>3.426793573788811</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684175405425256</v>
+        <v>4.655348351420287</v>
       </c>
       <c r="K8" t="n">
-        <v>12.62482011017735</v>
+        <v>16.51217638843167</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6112030084574</v>
+        <v>42.28764863504382</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81552755788593</v>
+        <v>99.8859296164697</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.16769121373427</v>
+        <v>81.63175596858846</v>
       </c>
       <c r="C9" t="n">
-        <v>41.23236412012162</v>
+        <v>39.76219372884115</v>
       </c>
       <c r="D9" t="n">
-        <v>1.866315339660167</v>
+        <v>1.856750390192597</v>
       </c>
       <c r="E9" t="n">
-        <v>9.815900540534237</v>
+        <v>8.773564732237958</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508261677114876</v>
+        <v>0.7457253075047361</v>
       </c>
       <c r="G9" t="n">
-        <v>28.87403878608053</v>
+        <v>28.43257310869579</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53800371472843</v>
+        <v>34.30336414521786</v>
       </c>
       <c r="I9" t="n">
-        <v>4.629943116822635</v>
+        <v>2.858995112834933</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692663548196795</v>
+        <v>4.6607831719046</v>
       </c>
       <c r="K9" t="n">
-        <v>14.83230878626572</v>
+        <v>18.36824403141153</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78127481283017</v>
+        <v>41.77437352936428</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84594771921751</v>
+        <v>99.90481128961696</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.79097502159101</v>
+        <v>86.05290923186516</v>
       </c>
       <c r="C10" t="n">
-        <v>39.57341229695739</v>
+        <v>42.81970101558127</v>
       </c>
       <c r="D10" t="n">
-        <v>1.759677279690749</v>
+        <v>1.85884496037506</v>
       </c>
       <c r="E10" t="n">
-        <v>9.899084941671161</v>
+        <v>10.53339141637831</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519943341526002</v>
+        <v>0.7465665482022784</v>
       </c>
       <c r="G10" t="n">
-        <v>27.22422569490697</v>
+        <v>29.72920230504397</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59173937101961</v>
+        <v>35.6066160862912</v>
       </c>
       <c r="I10" t="n">
-        <v>3.864288811696165</v>
+        <v>2.912246989310098</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699964588453749</v>
+        <v>4.66604092626424</v>
       </c>
       <c r="K10" t="n">
-        <v>17.209024978409</v>
+        <v>13.94709076813484</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08895319361076</v>
+        <v>43.13624270187385</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87139046897714</v>
+        <v>99.90303448558996</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.34335918198552</v>
+        <v>85.792569375653</v>
       </c>
       <c r="C11" t="n">
-        <v>37.72407319021825</v>
+        <v>42.93122220424173</v>
       </c>
       <c r="D11" t="n">
-        <v>1.651114626772972</v>
+        <v>1.843548286537301</v>
       </c>
       <c r="E11" t="n">
-        <v>9.825789275326683</v>
+        <v>10.87957168547849</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530003672737516</v>
+        <v>0.7472889256366774</v>
       </c>
       <c r="G11" t="n">
-        <v>25.54463694350204</v>
+        <v>29.50235353662794</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63801689459257</v>
+        <v>35.6588656852711</v>
       </c>
       <c r="I11" t="n">
-        <v>3.22454877905656</v>
+        <v>2.490385470872246</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706252295460946</v>
+        <v>4.670555785229234</v>
       </c>
       <c r="K11" t="n">
-        <v>19.65664081801448</v>
+        <v>14.20743062434701</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51194463588682</v>
+        <v>42.77841456792959</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89265864411955</v>
+        <v>99.91706739651832</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.81970091400562</v>
+        <v>83.95344176633336</v>
       </c>
       <c r="C12" t="n">
-        <v>35.69873694198674</v>
+        <v>41.47952169591526</v>
       </c>
       <c r="D12" t="n">
-        <v>1.540335542804768</v>
+        <v>1.764706779948181</v>
       </c>
       <c r="E12" t="n">
-        <v>9.614912608164634</v>
+        <v>10.76046614667135</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538680725607427</v>
+        <v>0.7479051971866764</v>
       </c>
       <c r="G12" t="n">
-        <v>23.83075746171691</v>
+        <v>28.24065075523702</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67793133779416</v>
+        <v>35.68827271068412</v>
       </c>
       <c r="I12" t="n">
-        <v>2.690220437459763</v>
+        <v>2.077032694189267</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71167545350464</v>
+        <v>4.674407482416727</v>
       </c>
       <c r="K12" t="n">
-        <v>22.18029908599438</v>
+        <v>16.04655823366665</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03139317260066</v>
+        <v>42.40474269622721</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91042920058177</v>
+        <v>99.93082262580911</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.28289260336771</v>
+        <v>85.01691996695868</v>
       </c>
       <c r="C13" t="n">
-        <v>33.57670710203411</v>
+        <v>42.38977428000901</v>
       </c>
       <c r="D13" t="n">
-        <v>1.430066531816328</v>
+        <v>1.766038018529456</v>
       </c>
       <c r="E13" t="n">
-        <v>9.300616537106192</v>
+        <v>11.36727177108961</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546171310483727</v>
+        <v>0.7484693930434294</v>
       </c>
       <c r="G13" t="n">
-        <v>22.12476939393267</v>
+        <v>28.5399725927663</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71238802822514</v>
+        <v>35.99321279697772</v>
       </c>
       <c r="I13" t="n">
-        <v>2.244077912186696</v>
+        <v>1.924021688030735</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716357069052327</v>
+        <v>4.677933706521434</v>
       </c>
       <c r="K13" t="n">
-        <v>24.71710739663229</v>
+        <v>14.98308003304129</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63145715584861</v>
+        <v>42.56305997490177</v>
       </c>
       <c r="M13" t="n">
-        <v>99.925271654515</v>
+        <v>99.93591428795207</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.66492735694052</v>
+        <v>83.09276318897427</v>
       </c>
       <c r="C14" t="n">
-        <v>38.19156817764269</v>
+        <v>40.76482023189307</v>
       </c>
       <c r="D14" t="n">
-        <v>1.431740089362822</v>
+        <v>1.685579909583696</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84678058916506</v>
+        <v>11.1167927197128</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555002334539475</v>
+        <v>0.7489511164330448</v>
       </c>
       <c r="G14" t="n">
-        <v>24.20224154086701</v>
+        <v>27.23973318677104</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80459103116451</v>
+        <v>36.01637843692621</v>
       </c>
       <c r="I14" t="n">
-        <v>2.902197413840002</v>
+        <v>1.604383341840937</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721876459087169</v>
+        <v>4.68094447770653</v>
       </c>
       <c r="K14" t="n">
-        <v>17.33507264305946</v>
+        <v>16.90723681102574</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37673234455573</v>
+        <v>42.27449791019144</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90337316525789</v>
+        <v>99.94655495311025</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.79227145758962</v>
+        <v>82.21432479564534</v>
       </c>
       <c r="C15" t="n">
-        <v>37.73994017519401</v>
+        <v>40.1083208700188</v>
       </c>
       <c r="D15" t="n">
-        <v>1.396716434635678</v>
+        <v>1.648186685106215</v>
       </c>
       <c r="E15" t="n">
-        <v>11.98723749399666</v>
+        <v>11.09750794637734</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562456088390843</v>
+        <v>0.7493653039953703</v>
       </c>
       <c r="G15" t="n">
-        <v>23.63697480549315</v>
+        <v>26.63544177823664</v>
       </c>
       <c r="H15" t="n">
-        <v>36.86767812820634</v>
+        <v>36.0362963403264</v>
       </c>
       <c r="I15" t="n">
-        <v>2.420883931174449</v>
+        <v>1.36399359163229</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726535055244274</v>
+        <v>4.683533149971064</v>
       </c>
       <c r="K15" t="n">
-        <v>18.20772854241036</v>
+        <v>17.78567520435466</v>
       </c>
       <c r="L15" t="n">
-        <v>43.97171468756673</v>
+        <v>42.06056260269126</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9193834051711</v>
+        <v>99.95455867706472</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.15368705774775</v>
+        <v>79.96346201664163</v>
       </c>
       <c r="C16" t="n">
-        <v>35.47482382245246</v>
+        <v>38.06908248910524</v>
       </c>
       <c r="D16" t="n">
-        <v>1.298271551068571</v>
+        <v>1.554719820754394</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47885978869176</v>
+        <v>10.65771376776387</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568886404229558</v>
+        <v>0.7497205405507213</v>
       </c>
       <c r="G16" t="n">
-        <v>21.97096789463984</v>
+        <v>25.12497500518609</v>
       </c>
       <c r="H16" t="n">
-        <v>36.89902651712041</v>
+        <v>36.05337934338419</v>
       </c>
       <c r="I16" t="n">
-        <v>2.019118663160726</v>
+        <v>1.137200160560363</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730554002643471</v>
+        <v>4.685753378442008</v>
       </c>
       <c r="K16" t="n">
-        <v>20.84631294225226</v>
+        <v>20.03653798335836</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61161645942933</v>
+        <v>41.8564908166577</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93275322413405</v>
+        <v>99.96211128912131</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.07501640234396</v>
+        <v>84.40872726417783</v>
       </c>
       <c r="C17" t="n">
-        <v>36.86320492340675</v>
+        <v>41.01264219588698</v>
       </c>
       <c r="D17" t="n">
-        <v>1.299341734472578</v>
+        <v>1.555491987530829</v>
       </c>
       <c r="E17" t="n">
-        <v>12.33506847227561</v>
+        <v>12.23129609449852</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757512554319086</v>
+        <v>0.7500928965760939</v>
       </c>
       <c r="G17" t="n">
-        <v>22.50166901792072</v>
+        <v>26.49613054640098</v>
       </c>
       <c r="H17" t="n">
-        <v>37.44203304798623</v>
+        <v>37.42996258329872</v>
       </c>
       <c r="I17" t="n">
-        <v>2.004938110875454</v>
+        <v>1.257672552272086</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734453464494285</v>
+        <v>4.688080603600587</v>
       </c>
       <c r="K17" t="n">
-        <v>18.92498359765604</v>
+        <v>15.59127273582219</v>
       </c>
       <c r="L17" t="n">
-        <v>44.1450352531519</v>
+        <v>43.35418346072422</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9332237742147</v>
+        <v>99.95809839243337</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.5057237554678</v>
+        <v>85.95014969966164</v>
       </c>
       <c r="C18" t="n">
-        <v>34.60276275862231</v>
+        <v>41.72995248069039</v>
       </c>
       <c r="D18" t="n">
-        <v>1.20781474654664</v>
+        <v>1.556720180931151</v>
       </c>
       <c r="E18" t="n">
-        <v>11.74483468628373</v>
+        <v>12.81905618321621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580503226035161</v>
+        <v>0.7506851588009</v>
       </c>
       <c r="G18" t="n">
-        <v>20.91662796684367</v>
+        <v>26.63644030922923</v>
       </c>
       <c r="H18" t="n">
-        <v>37.46861364755912</v>
+        <v>37.45951672654576</v>
       </c>
       <c r="I18" t="n">
-        <v>1.671967869359144</v>
+        <v>2.03594889843277</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737814516271973</v>
+        <v>4.691782242505625</v>
       </c>
       <c r="K18" t="n">
-        <v>21.4942762445322</v>
+        <v>14.04985030033836</v>
       </c>
       <c r="L18" t="n">
-        <v>43.84726827154339</v>
+        <v>44.15238579858185</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94430727469791</v>
+        <v>99.9321885796106</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.54042032526714</v>
+        <v>83.45021752809052</v>
       </c>
       <c r="C19" t="n">
-        <v>33.89048850298754</v>
+        <v>39.54574034094426</v>
       </c>
       <c r="D19" t="n">
-        <v>1.173940521736253</v>
+        <v>1.462820420584064</v>
       </c>
       <c r="E19" t="n">
-        <v>11.64840355754382</v>
+        <v>12.32878634138263</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585058211152315</v>
+        <v>0.7511942424517184</v>
       </c>
       <c r="G19" t="n">
-        <v>20.33000277448704</v>
+        <v>25.02975762330168</v>
       </c>
       <c r="H19" t="n">
-        <v>37.49112784911487</v>
+        <v>37.48492022268454</v>
       </c>
       <c r="I19" t="n">
-        <v>1.397778419299705</v>
+        <v>1.697774662362645</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740661381970193</v>
+        <v>4.69496401532324</v>
       </c>
       <c r="K19" t="n">
-        <v>22.45957967473288</v>
+        <v>16.54978247190948</v>
       </c>
       <c r="L19" t="n">
-        <v>43.60336718813609</v>
+        <v>43.84792305107869</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95343536585651</v>
+        <v>99.94344586393242</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.94118437341143</v>
+        <v>80.88776766271296</v>
       </c>
       <c r="C20" t="n">
-        <v>31.50575261459606</v>
+        <v>37.24591079878179</v>
       </c>
       <c r="D20" t="n">
-        <v>1.082461153837158</v>
+        <v>1.367062281653479</v>
       </c>
       <c r="E20" t="n">
-        <v>10.93493771288681</v>
+        <v>11.75766745193237</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588990082173657</v>
+        <v>0.7516324705604507</v>
       </c>
       <c r="G20" t="n">
-        <v>18.74578639489882</v>
+        <v>23.39127693615484</v>
       </c>
       <c r="H20" t="n">
-        <v>37.5105621467885</v>
+        <v>37.50678799637987</v>
       </c>
       <c r="I20" t="n">
-        <v>1.165419155424245</v>
+        <v>1.415637585029135</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743118801358532</v>
+        <v>4.697702941002817</v>
       </c>
       <c r="K20" t="n">
-        <v>25.05881562658856</v>
+        <v>19.11223233728704</v>
       </c>
       <c r="L20" t="n">
-        <v>43.39660458050148</v>
+        <v>43.59469645664332</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96117282168612</v>
+        <v>99.95283959271215</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.44647046372278</v>
+        <v>78.39516914649256</v>
       </c>
       <c r="C21" t="n">
-        <v>35.6122535822147</v>
+        <v>34.97165695533479</v>
       </c>
       <c r="D21" t="n">
-        <v>1.083177657813339</v>
+        <v>1.274385250714812</v>
       </c>
       <c r="E21" t="n">
-        <v>13.12339198277447</v>
+        <v>11.15729681860562</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594013395527491</v>
+        <v>0.7520096810088934</v>
       </c>
       <c r="G21" t="n">
-        <v>20.6698551073802</v>
+        <v>21.80551590287921</v>
       </c>
       <c r="H21" t="n">
-        <v>39.4470516619848</v>
+        <v>37.52561096222275</v>
       </c>
       <c r="I21" t="n">
-        <v>1.617334342012535</v>
+        <v>1.180290024755679</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746258372204679</v>
+        <v>4.700060506305584</v>
       </c>
       <c r="K21" t="n">
-        <v>18.55352953627722</v>
+        <v>21.60483085350743</v>
       </c>
       <c r="L21" t="n">
-        <v>45.78034139809846</v>
+        <v>43.38418892490697</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94612451659039</v>
+        <v>99.9606767337492</v>
       </c>
     </row>
   </sheetData>
